--- a/Librairies/TEP-AltiumLib-Passives-RLC.xlsx
+++ b/Librairies/TEP-AltiumLib-Passives-RLC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/Altium/243-TEP_Altium-Lib/Librairies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1440" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11D1E836-EED1-4A21-BDD9-16E427D43CEB}"/>
+  <xr:revisionPtr revIDLastSave="1459" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D965C3-5381-474B-81A7-B51BBC378035}"/>
   <bookViews>
-    <workbookView xWindow="696" yWindow="636" windowWidth="19380" windowHeight="9516" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cap" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="476">
   <si>
     <t>Comment</t>
   </si>
@@ -1453,6 +1453,24 @@
   </si>
   <si>
     <t>311-1036-1-ND</t>
+  </si>
+  <si>
+    <t>RES048</t>
+  </si>
+  <si>
+    <t>Res 22R 1% 0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-0722RL</t>
+  </si>
+  <si>
+    <t>22R</t>
+  </si>
+  <si>
+    <t>C114765</t>
+  </si>
+  <si>
+    <t>311-22.0LRCT-ND</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1546,7 +1564,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1830,25 +1847,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" customWidth="1"/>
+    <col min="4" max="4" width="39.6328125" customWidth="1"/>
+    <col min="5" max="5" width="14.36328125" customWidth="1"/>
+    <col min="6" max="6" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" customWidth="1"/>
+    <col min="9" max="9" width="16.08984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.44140625" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" customWidth="1"/>
-    <col min="15" max="15" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" customWidth="1"/>
-    <col min="17" max="17" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.453125" customWidth="1"/>
+    <col min="14" max="14" width="21.6328125" customWidth="1"/>
+    <col min="15" max="15" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.36328125" customWidth="1"/>
+    <col min="17" max="17" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -1907,7 +1924,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1957,7 +1974,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -2007,7 +2024,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2057,7 +2074,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -2108,7 +2125,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -2159,7 +2176,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -2206,7 +2223,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>106</v>
       </c>
@@ -2253,7 +2270,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -2303,7 +2320,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>113</v>
       </c>
@@ -2350,7 +2367,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -2397,7 +2414,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>161</v>
       </c>
@@ -2447,7 +2464,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>163</v>
       </c>
@@ -2492,7 +2509,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>169</v>
       </c>
@@ -2537,7 +2554,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>186</v>
       </c>
@@ -2584,7 +2601,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>187</v>
       </c>
@@ -2631,7 +2648,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>195</v>
       </c>
@@ -2678,7 +2695,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>198</v>
       </c>
@@ -2725,7 +2742,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>199</v>
       </c>
@@ -2772,7 +2789,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>200</v>
       </c>
@@ -2819,7 +2836,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>252</v>
       </c>
@@ -2866,7 +2883,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>319</v>
       </c>
@@ -2913,7 +2930,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>364</v>
       </c>
@@ -2960,7 +2977,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>421</v>
       </c>
@@ -3001,7 +3018,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>431</v>
       </c>
@@ -3036,7 +3053,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>432</v>
       </c>
@@ -3071,7 +3088,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>433</v>
       </c>
@@ -3106,11 +3123,11 @@
         <v>457</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>464</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" t="s">
         <v>465</v>
       </c>
       <c r="E28" t="s">
@@ -3168,27 +3185,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0837104-CD0C-4055-94B3-0A98F94F86E8}">
-  <dimension ref="A1:S48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S49"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.77734375" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" customWidth="1"/>
-    <col min="13" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="22.21875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" customWidth="1"/>
-    <col min="17" max="17" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="26.08984375" customWidth="1"/>
+    <col min="5" max="5" width="14.36328125" customWidth="1"/>
+    <col min="6" max="6" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.81640625" customWidth="1"/>
+    <col min="11" max="11" width="6.453125" customWidth="1"/>
+    <col min="12" max="12" width="11.453125" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" customWidth="1"/>
+    <col min="14" max="14" width="22.1796875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.54296875" customWidth="1"/>
+    <col min="17" max="17" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -3247,7 +3264,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3297,7 +3314,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -3344,7 +3361,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -3391,7 +3408,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -3438,7 +3455,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -3482,7 +3499,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -3532,7 +3549,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -3582,7 +3599,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -3638,7 +3655,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -3691,7 +3708,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -3738,7 +3755,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -3788,7 +3805,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -3838,7 +3855,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>157</v>
       </c>
@@ -3885,7 +3902,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>171</v>
       </c>
@@ -3941,7 +3958,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>176</v>
       </c>
@@ -3988,7 +4005,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>181</v>
       </c>
@@ -4038,7 +4055,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>209</v>
       </c>
@@ -4085,7 +4102,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>236</v>
       </c>
@@ -4138,7 +4155,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>272</v>
       </c>
@@ -4188,7 +4205,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>274</v>
       </c>
@@ -4238,7 +4255,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>278</v>
       </c>
@@ -4288,7 +4305,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>283</v>
       </c>
@@ -4338,7 +4355,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>284</v>
       </c>
@@ -4388,7 +4405,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>285</v>
       </c>
@@ -4438,7 +4455,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>288</v>
       </c>
@@ -4488,7 +4505,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>290</v>
       </c>
@@ -4535,7 +4552,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>314</v>
       </c>
@@ -4582,7 +4599,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>343</v>
       </c>
@@ -4629,7 +4646,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>347</v>
       </c>
@@ -4676,7 +4693,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>366</v>
       </c>
@@ -4723,7 +4740,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>367</v>
       </c>
@@ -4770,7 +4787,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>379</v>
       </c>
@@ -4811,7 +4828,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>380</v>
       </c>
@@ -4852,7 +4869,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>381</v>
       </c>
@@ -4893,7 +4910,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>382</v>
       </c>
@@ -4934,7 +4951,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>396</v>
       </c>
@@ -4975,7 +4992,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>397</v>
       </c>
@@ -5016,7 +5033,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>398</v>
       </c>
@@ -5057,7 +5074,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>399</v>
       </c>
@@ -5098,7 +5115,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>400</v>
       </c>
@@ -5139,7 +5156,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>401</v>
       </c>
@@ -5180,7 +5197,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>402</v>
       </c>
@@ -5221,7 +5238,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>451</v>
       </c>
@@ -5262,7 +5279,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>452</v>
       </c>
@@ -5303,7 +5320,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>453</v>
       </c>
@@ -5344,7 +5361,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>455</v>
       </c>
@@ -5385,7 +5402,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>458</v>
       </c>
@@ -5437,6 +5454,59 @@
       </c>
       <c r="S48" t="s">
         <v>463</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>470</v>
+      </c>
+      <c r="D49" t="s">
+        <v>471</v>
+      </c>
+      <c r="E49" t="s">
+        <v>67</v>
+      </c>
+      <c r="F49" t="s">
+        <v>472</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I49" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" t="s">
+        <v>11</v>
+      </c>
+      <c r="K49" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" t="s">
+        <v>456</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O49" t="s">
+        <v>457</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>474</v>
+      </c>
+      <c r="R49" t="s">
+        <v>81</v>
+      </c>
+      <c r="S49" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -5449,23 +5519,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A0C756-8EF7-43C5-A896-F15EFC0CC7A5}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="33.77734375" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" customWidth="1"/>
-    <col min="9" max="9" width="19.6640625" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" customWidth="1"/>
+    <col min="1" max="3" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="33.81640625" customWidth="1"/>
+    <col min="5" max="5" width="14.36328125" customWidth="1"/>
+    <col min="6" max="6" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1796875" customWidth="1"/>
+    <col min="9" max="9" width="19.6328125" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" customWidth="1"/>
+    <col min="12" max="12" width="11.453125" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="15" max="15" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -5524,7 +5594,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5574,7 +5644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -5621,7 +5691,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>147</v>
       </c>
@@ -5668,7 +5738,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>214</v>
       </c>
@@ -5715,7 +5785,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>215</v>
       </c>

--- a/Librairies/TEP-AltiumLib-Passives-RLC.xlsx
+++ b/Librairies/TEP-AltiumLib-Passives-RLC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/Altium/243-TEP_Altium-Lib/Librairies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1459" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D965C3-5381-474B-81A7-B51BBC378035}"/>
+  <xr:revisionPtr revIDLastSave="1562" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43DFC5E3-FF3D-4C85-8DC1-9BE80E6BA70C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="16490" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cap" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="492">
   <si>
     <t>Comment</t>
   </si>
@@ -180,9 +180,6 @@
     <t>LCSC</t>
   </si>
   <si>
-    <t>1uH</t>
-  </si>
-  <si>
     <t>2.3A</t>
   </si>
   <si>
@@ -267,18 +264,6 @@
     <t>Taiyo Yuden</t>
   </si>
   <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>470pF</t>
-  </si>
-  <si>
     <t>X5R</t>
   </si>
   <si>
@@ -369,12 +354,6 @@
     <t>Saturation Current</t>
   </si>
   <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
     <t>CAP008</t>
   </si>
   <si>
@@ -390,9 +369,6 @@
     <t>16V</t>
   </si>
   <si>
-    <t>470nF</t>
-  </si>
-  <si>
     <t>C105526</t>
   </si>
   <si>
@@ -426,9 +402,6 @@
     <t>CAP010</t>
   </si>
   <si>
-    <t>22pF</t>
-  </si>
-  <si>
     <t>C106203</t>
   </si>
   <si>
@@ -531,18 +504,12 @@
     <t>CAP011</t>
   </si>
   <si>
-    <t>1uF</t>
-  </si>
-  <si>
     <t>CAP012</t>
   </si>
   <si>
     <t>COND0002SM</t>
   </si>
   <si>
-    <t>22pf</t>
-  </si>
-  <si>
     <t>12065A220KAT2A</t>
   </si>
   <si>
@@ -615,12 +582,6 @@
     <t>CC0402JRNPO9BN100</t>
   </si>
   <si>
-    <t>10pF</t>
-  </si>
-  <si>
-    <t>100pF</t>
-  </si>
-  <si>
     <t>C106199</t>
   </si>
   <si>
@@ -648,12 +609,6 @@
     <t>CAP019</t>
   </si>
   <si>
-    <t>1.2pF</t>
-  </si>
-  <si>
-    <t>0.8pF</t>
-  </si>
-  <si>
     <t>CC0402BRNPO9BN1R2</t>
   </si>
   <si>
@@ -702,9 +657,6 @@
     <t>Inductor 10uH, 3mA, 1.85Ω 0603</t>
   </si>
   <si>
-    <t>10uH</t>
-  </si>
-  <si>
     <t>C411950</t>
   </si>
   <si>
@@ -732,9 +684,6 @@
     <t>750mA</t>
   </si>
   <si>
-    <t>3.6nH</t>
-  </si>
-  <si>
     <t>0R140</t>
   </si>
   <si>
@@ -1128,9 +1077,6 @@
     <t>Res 100R 1% 0603</t>
   </si>
   <si>
-    <t>2.2uF</t>
-  </si>
-  <si>
     <t>C100082</t>
   </si>
   <si>
@@ -1356,9 +1302,6 @@
     <t>CAP CER 10uF 50V X7R 1206</t>
   </si>
   <si>
-    <t>18pF</t>
-  </si>
-  <si>
     <t>RESI0045SMT</t>
   </si>
   <si>
@@ -1446,9 +1389,6 @@
     <t>CC0402KRX7R9BB102</t>
   </si>
   <si>
-    <t>1nF</t>
-  </si>
-  <si>
     <t>C106205</t>
   </si>
   <si>
@@ -1471,6 +1411,114 @@
   </si>
   <si>
     <t>311-22.0LRCT-ND</t>
+  </si>
+  <si>
+    <t>100n</t>
+  </si>
+  <si>
+    <t>4u7</t>
+  </si>
+  <si>
+    <t>10u</t>
+  </si>
+  <si>
+    <t>100u</t>
+  </si>
+  <si>
+    <t>470p</t>
+  </si>
+  <si>
+    <t>10n</t>
+  </si>
+  <si>
+    <t>470n</t>
+  </si>
+  <si>
+    <t>22p</t>
+  </si>
+  <si>
+    <t>1u</t>
+  </si>
+  <si>
+    <t>10p</t>
+  </si>
+  <si>
+    <t>100p</t>
+  </si>
+  <si>
+    <t>1p2</t>
+  </si>
+  <si>
+    <t>0p8p</t>
+  </si>
+  <si>
+    <t>2u2</t>
+  </si>
+  <si>
+    <t>18p</t>
+  </si>
+  <si>
+    <t>1n</t>
+  </si>
+  <si>
+    <t>3n6</t>
+  </si>
+  <si>
+    <t>RES049</t>
+  </si>
+  <si>
+    <t>Res 330R 1% 0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-07330RL</t>
+  </si>
+  <si>
+    <t>C105875</t>
+  </si>
+  <si>
+    <t>311-330LRCT-ND</t>
+  </si>
+  <si>
+    <t>RES050</t>
+  </si>
+  <si>
+    <t>Res 330R 1% 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-07330RL</t>
+  </si>
+  <si>
+    <t>C105881</t>
+  </si>
+  <si>
+    <t>311-330HRCT-ND</t>
+  </si>
+  <si>
+    <t>RES051</t>
+  </si>
+  <si>
+    <t>RES052</t>
+  </si>
+  <si>
+    <t>Res 270R 1% 0402</t>
+  </si>
+  <si>
+    <t>Res 270R 1% 0603</t>
+  </si>
+  <si>
+    <t>RC0402FR-07270RL</t>
+  </si>
+  <si>
+    <t>RC0603FR-07270RL</t>
+  </si>
+  <si>
+    <t>C137754</t>
+  </si>
+  <si>
+    <t>311-270LRCT-ND</t>
+  </si>
+  <si>
+    <t>C163474</t>
   </si>
 </sst>
 </file>
@@ -1581,6 +1629,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1870,19 +1922,19 @@
         <v>5</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1</v>
@@ -1897,7 +1949,7 @@
         <v>4</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>15</v>
@@ -1918,10 +1970,10 @@
         <v>42</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
@@ -1929,22 +1981,22 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="G2" t="s">
-        <v>109</v>
+        <v>456</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -1959,19 +2011,19 @@
         <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N2" t="s">
         <v>29</v>
       </c>
       <c r="O2" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P2" t="s">
         <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -1979,22 +2031,22 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G3" t="s">
-        <v>109</v>
+        <v>456</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
@@ -2009,19 +2061,19 @@
         <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N3" t="s">
         <v>30</v>
       </c>
       <c r="O3" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P3" t="s">
         <v>44</v>
       </c>
       <c r="Q3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -2029,25 +2081,25 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>457</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
         <v>12</v>
@@ -2059,19 +2111,19 @@
         <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P4" t="s">
         <v>44</v>
       </c>
       <c r="Q4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -2079,26 +2131,26 @@
         <v>24</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="E5" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="F5" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>458</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" t="s">
         <v>12</v>
@@ -2110,49 +2162,49 @@
         <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O5" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P5" t="s">
         <v>44</v>
       </c>
       <c r="Q5" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="3" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>459</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
@@ -2161,45 +2213,45 @@
         <v>21</v>
       </c>
       <c r="M6" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O6" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P6" t="s">
         <v>44</v>
       </c>
       <c r="Q6" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>460</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I7" t="s">
         <v>11</v>
       </c>
       <c r="J7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K7" t="s">
         <v>13</v>
@@ -2208,39 +2260,39 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
       </c>
       <c r="O7" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P7" t="s">
         <v>44</v>
       </c>
       <c r="Q7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G8" t="s">
-        <v>108</v>
+        <v>461</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I8" t="s">
         <v>11</v>
@@ -2255,42 +2307,42 @@
         <v>21</v>
       </c>
       <c r="M8" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
       </c>
       <c r="O8" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P8" t="s">
         <v>44</v>
       </c>
       <c r="Q8" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G9" t="s">
-        <v>109</v>
+        <v>456</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I9" t="s">
         <v>11</v>
@@ -2305,42 +2357,42 @@
         <v>21</v>
       </c>
       <c r="M9" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O9" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P9" t="s">
         <v>44</v>
       </c>
       <c r="Q9" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>115</v>
+        <v>462</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I10" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J10" t="s">
         <v>12</v>
@@ -2352,45 +2404,45 @@
         <v>21</v>
       </c>
       <c r="M10" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N10" t="s">
         <v>30</v>
       </c>
       <c r="O10" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P10" t="s">
         <v>44</v>
       </c>
       <c r="Q10" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G11" t="s">
-        <v>127</v>
+        <v>463</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K11" t="s">
         <v>13</v>
@@ -2399,42 +2451,42 @@
         <v>21</v>
       </c>
       <c r="M11" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P11" t="s">
         <v>44</v>
       </c>
       <c r="Q11" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="G12" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I12" t="s">
         <v>11</v>
@@ -2449,49 +2501,49 @@
         <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O12" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P12" t="s">
         <v>44</v>
       </c>
       <c r="Q12" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="6" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G13" t="s">
-        <v>165</v>
+        <v>463</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I13" t="s">
         <v>11</v>
       </c>
       <c r="J13" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K13" t="s">
         <v>13</v>
@@ -2500,43 +2552,43 @@
         <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="O13" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G14" t="s">
-        <v>165</v>
+        <v>463</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I14" t="s">
         <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K14" t="s">
         <v>13</v>
@@ -2545,39 +2597,39 @@
         <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O14" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>465</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I15" t="s">
         <v>11</v>
       </c>
       <c r="J15" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K15" t="s">
         <v>13</v>
@@ -2586,45 +2638,45 @@
         <v>21</v>
       </c>
       <c r="M15" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
       </c>
       <c r="O15" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P15" t="s">
         <v>44</v>
       </c>
       <c r="Q15" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D16" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="G16" t="s">
-        <v>191</v>
+        <v>466</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I16" t="s">
         <v>11</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K16" t="s">
         <v>13</v>
@@ -2633,45 +2685,45 @@
         <v>21</v>
       </c>
       <c r="M16" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P16" t="s">
         <v>44</v>
       </c>
       <c r="Q16" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E17" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>457</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I17" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="J17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s">
         <v>13</v>
@@ -2680,39 +2732,39 @@
         <v>21</v>
       </c>
       <c r="M17" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
       </c>
       <c r="O17" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P17" t="s">
         <v>44</v>
       </c>
       <c r="Q17" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>461</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I18" t="s">
         <v>11</v>
@@ -2727,45 +2779,45 @@
         <v>21</v>
       </c>
       <c r="M18" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N18" t="s">
         <v>29</v>
       </c>
       <c r="O18" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P18" t="s">
         <v>44</v>
       </c>
       <c r="Q18" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="G19" t="s">
-        <v>201</v>
+        <v>467</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I19" t="s">
         <v>11</v>
       </c>
       <c r="J19" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K19" t="s">
         <v>13</v>
@@ -2774,45 +2826,45 @@
         <v>21</v>
       </c>
       <c r="M19" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N19" t="s">
         <v>29</v>
       </c>
       <c r="O19" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P19" t="s">
         <v>44</v>
       </c>
       <c r="Q19" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="G20" t="s">
-        <v>202</v>
+        <v>468</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I20" t="s">
         <v>11</v>
       </c>
       <c r="J20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K20" t="s">
         <v>13</v>
@@ -2821,45 +2873,45 @@
         <v>21</v>
       </c>
       <c r="M20" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N20" t="s">
         <v>29</v>
       </c>
       <c r="O20" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P20" t="s">
         <v>44</v>
       </c>
       <c r="Q20" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>458</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s">
         <v>13</v>
@@ -2868,89 +2920,89 @@
         <v>21</v>
       </c>
       <c r="M21" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N21" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O21" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P21" t="s">
         <v>44</v>
       </c>
       <c r="Q21" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="E22" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="F22" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>459</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I22" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="J22" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="K22" t="s">
         <v>13</v>
       </c>
       <c r="L22" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="M22" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N22" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="O22" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P22" t="s">
         <v>44</v>
       </c>
       <c r="Q22" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="G23" t="s">
-        <v>361</v>
+        <v>469</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J23" t="s">
         <v>12</v>
@@ -2962,39 +3014,39 @@
         <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N23" t="s">
         <v>30</v>
       </c>
       <c r="O23" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P23" t="s">
         <v>44</v>
       </c>
       <c r="Q23" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="B24" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C24" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>458</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I24" t="s">
         <v>11</v>
@@ -3009,30 +3061,30 @@
         <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O24" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="B25" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="C25" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="D25" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="G25" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="I25" t="s">
         <v>11</v>
@@ -3044,30 +3096,30 @@
         <v>21</v>
       </c>
       <c r="M25" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N25" t="s">
         <v>30</v>
       </c>
       <c r="O25" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="B26" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="C26" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="D26" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="G26" t="s">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="I26" t="s">
         <v>11</v>
@@ -3079,33 +3131,33 @@
         <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N26" t="s">
         <v>30</v>
       </c>
       <c r="O26" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B27" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="C27" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D27" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>458</v>
       </c>
       <c r="I27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K27" t="s">
         <v>13</v>
@@ -3114,33 +3166,33 @@
         <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="O27" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="D28" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F28" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="G28" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I28" t="s">
         <v>11</v>
@@ -3155,25 +3207,25 @@
         <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
       </c>
       <c r="O28" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P28" t="s">
         <v>44</v>
       </c>
       <c r="Q28" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="R28" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S28" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -3185,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0837104-CD0C-4055-94B3-0A98F94F86E8}">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" customWidth="1"/>
@@ -3210,19 +3262,19 @@
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1</v>
@@ -3237,7 +3289,7 @@
         <v>20</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>15</v>
@@ -3258,10 +3310,10 @@
         <v>42</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
@@ -3269,28 +3321,28 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K2" t="s">
         <v>13</v>
@@ -3299,19 +3351,19 @@
         <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O2" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P2" t="s">
         <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -3319,25 +3371,25 @@
         <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="G3" t="s">
         <v>35</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I3" t="s">
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K3" t="s">
         <v>13</v>
@@ -3346,19 +3398,19 @@
         <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O3" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P3" t="s">
         <v>44</v>
       </c>
       <c r="Q3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -3366,19 +3418,19 @@
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
@@ -3393,19 +3445,19 @@
         <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O4" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P4" t="s">
         <v>44</v>
       </c>
       <c r="Q4" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -3413,19 +3465,19 @@
         <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G5" t="s">
         <v>35</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I5" t="s">
         <v>36</v>
@@ -3440,19 +3492,19 @@
         <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O5" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P5" t="s">
         <v>44</v>
       </c>
       <c r="Q5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
@@ -3460,19 +3512,19 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J6" t="s">
         <v>11</v>
@@ -3484,42 +3536,42 @@
         <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O6" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P6" t="s">
         <v>44</v>
       </c>
       <c r="Q6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" t="s">
         <v>67</v>
       </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I7" t="s">
         <v>36</v>
@@ -3534,42 +3586,42 @@
         <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O7" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P7" t="s">
         <v>44</v>
       </c>
       <c r="Q7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I8" t="s">
         <v>36</v>
@@ -3584,42 +3636,42 @@
         <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O8" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I9" t="s">
         <v>36</v>
@@ -3634,45 +3686,45 @@
         <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O9" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I10" t="s">
         <v>36</v>
@@ -3687,45 +3739,45 @@
         <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O10" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q10" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="R10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="G11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I11" t="s">
         <v>36</v>
@@ -3740,42 +3792,42 @@
         <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O11" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P11" t="s">
         <v>44</v>
       </c>
       <c r="Q11" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="G12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I12" t="s">
         <v>36</v>
@@ -3790,42 +3842,42 @@
         <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O12" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P12" t="s">
         <v>44</v>
       </c>
       <c r="Q12" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I13" t="s">
         <v>36</v>
@@ -3840,39 +3892,39 @@
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O13" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P13" t="s">
         <v>44</v>
       </c>
       <c r="Q13" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="G14" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I14" t="s">
         <v>36</v>
@@ -3887,48 +3939,48 @@
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O14" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P14" t="s">
         <v>44</v>
       </c>
       <c r="Q14" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="G15" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I15" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J15" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K15" t="s">
         <v>13</v>
@@ -3937,51 +3989,51 @@
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O15" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P15" t="s">
         <v>44</v>
       </c>
       <c r="Q15" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="R15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S15" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I16" t="s">
         <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K16" t="s">
         <v>13</v>
@@ -3990,48 +4042,48 @@
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O16" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P16" t="s">
         <v>44</v>
       </c>
       <c r="Q16" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I17" t="s">
         <v>10</v>
       </c>
       <c r="J17" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K17" t="s">
         <v>13</v>
@@ -4040,39 +4092,39 @@
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O17" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P17" t="s">
         <v>44</v>
       </c>
       <c r="Q17" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G18" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I18" t="s">
         <v>36</v>
@@ -4087,45 +4139,45 @@
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O18" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P18" t="s">
         <v>44</v>
       </c>
       <c r="Q18" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I19" t="s">
         <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K19" t="s">
         <v>13</v>
@@ -4134,54 +4186,54 @@
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O19" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P19" t="s">
         <v>44</v>
       </c>
       <c r="Q19" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="R19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S19" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="D20" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I20" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J20" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K20" t="s">
         <v>13</v>
@@ -4190,48 +4242,48 @@
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P20" t="s">
         <v>44</v>
       </c>
       <c r="Q20" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D21" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I21" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J21" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K21" t="s">
         <v>13</v>
@@ -4240,48 +4292,48 @@
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O21" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P21" t="s">
         <v>44</v>
       </c>
       <c r="Q21" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="D22" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F22" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I22" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J22" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K22" t="s">
         <v>13</v>
@@ -4290,48 +4342,48 @@
         <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O22" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P22" t="s">
         <v>44</v>
       </c>
       <c r="Q22" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>266</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" t="s">
+        <v>425</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" t="s">
         <v>283</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="G23" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" t="s">
         <v>279</v>
-      </c>
-      <c r="D23" t="s">
-        <v>444</v>
-      </c>
-      <c r="E23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" t="s">
-        <v>300</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" t="s">
-        <v>296</v>
       </c>
       <c r="K23" t="s">
         <v>13</v>
@@ -4340,48 +4392,48 @@
         <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O23" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P23" t="s">
         <v>44</v>
       </c>
       <c r="Q23" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D24" t="s">
+        <v>424</v>
+      </c>
+      <c r="E24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" t="s">
         <v>284</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="D24" t="s">
-        <v>443</v>
-      </c>
-      <c r="E24" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" t="s">
-        <v>301</v>
-      </c>
       <c r="G24" s="9" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I24" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J24" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K24" t="s">
         <v>13</v>
@@ -4390,48 +4442,48 @@
         <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O24" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P24" t="s">
         <v>44</v>
       </c>
       <c r="Q24" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="D25" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I25" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J25" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K25" t="s">
         <v>13</v>
@@ -4440,48 +4492,48 @@
         <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O25" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P25" t="s">
         <v>44</v>
       </c>
       <c r="Q25" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="D26" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I26" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J26" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K26" t="s">
         <v>13</v>
@@ -4490,39 +4542,39 @@
         <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O26" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P26" t="s">
         <v>44</v>
       </c>
       <c r="Q26" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F27" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G27" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I27" t="s">
         <v>36</v>
@@ -4537,39 +4589,39 @@
         <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O27" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P27" t="s">
         <v>44</v>
       </c>
       <c r="Q27" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F28" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="G28" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I28" t="s">
         <v>36</v>
@@ -4584,39 +4636,39 @@
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O28" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P28" t="s">
         <v>44</v>
       </c>
       <c r="Q28" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F29" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I29" t="s">
         <v>36</v>
@@ -4631,45 +4683,45 @@
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O29" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P29" t="s">
         <v>44</v>
       </c>
       <c r="Q29" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I30" t="s">
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K30" t="s">
         <v>13</v>
@@ -4678,45 +4730,45 @@
         <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O30" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P30" t="s">
         <v>44</v>
       </c>
       <c r="Q30" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="D31" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I31" t="s">
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K31" t="s">
         <v>13</v>
@@ -4725,45 +4777,45 @@
         <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O31" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P31" t="s">
         <v>44</v>
       </c>
       <c r="Q31" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="D32" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I32" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J32" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K32" t="s">
         <v>13</v>
@@ -4772,45 +4824,45 @@
         <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O32" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P32" t="s">
         <v>44</v>
       </c>
       <c r="Q32" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C33" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D33" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I33" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J33" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K33" t="s">
         <v>13</v>
@@ -4819,39 +4871,39 @@
         <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O33" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s">
+        <v>367</v>
+      </c>
+      <c r="C34" t="s">
+        <v>366</v>
+      </c>
+      <c r="D34" t="s">
         <v>385</v>
       </c>
-      <c r="C34" t="s">
-        <v>384</v>
-      </c>
-      <c r="D34" t="s">
-        <v>403</v>
-      </c>
       <c r="G34" s="9" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I34" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J34" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K34" t="s">
         <v>13</v>
@@ -4860,39 +4912,39 @@
         <v>25</v>
       </c>
       <c r="M34" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O34" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35" t="s">
         <v>386</v>
       </c>
-      <c r="C35" t="s">
-        <v>384</v>
-      </c>
-      <c r="D35" t="s">
-        <v>404</v>
-      </c>
       <c r="G35" s="9" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I35" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J35" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K35" t="s">
         <v>13</v>
@@ -4901,39 +4953,39 @@
         <v>25</v>
       </c>
       <c r="M35" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O35" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s">
+        <v>369</v>
+      </c>
+      <c r="C36" t="s">
+        <v>366</v>
+      </c>
+      <c r="D36" t="s">
         <v>387</v>
       </c>
-      <c r="C36" t="s">
-        <v>384</v>
-      </c>
-      <c r="D36" t="s">
-        <v>405</v>
-      </c>
       <c r="G36" s="9" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I36" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J36" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K36" t="s">
         <v>13</v>
@@ -4942,39 +4994,39 @@
         <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O36" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="B37" t="s">
+        <v>370</v>
+      </c>
+      <c r="C37" t="s">
+        <v>366</v>
+      </c>
+      <c r="D37" t="s">
         <v>388</v>
       </c>
-      <c r="C37" t="s">
-        <v>384</v>
-      </c>
-      <c r="D37" t="s">
-        <v>406</v>
-      </c>
       <c r="G37" s="9" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I37" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J37" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K37" t="s">
         <v>13</v>
@@ -4983,39 +5035,39 @@
         <v>25</v>
       </c>
       <c r="M37" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O37" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s">
+        <v>371</v>
+      </c>
+      <c r="C38" t="s">
+        <v>366</v>
+      </c>
+      <c r="D38" t="s">
         <v>389</v>
       </c>
-      <c r="C38" t="s">
-        <v>384</v>
-      </c>
-      <c r="D38" t="s">
-        <v>407</v>
-      </c>
       <c r="G38" s="9" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I38" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J38" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K38" t="s">
         <v>13</v>
@@ -5024,39 +5076,39 @@
         <v>25</v>
       </c>
       <c r="M38" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O38" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s">
+        <v>372</v>
+      </c>
+      <c r="C39" t="s">
+        <v>366</v>
+      </c>
+      <c r="D39" t="s">
         <v>390</v>
       </c>
-      <c r="C39" t="s">
-        <v>384</v>
-      </c>
-      <c r="D39" t="s">
-        <v>408</v>
-      </c>
       <c r="G39" s="9" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I39" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J39" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K39" t="s">
         <v>13</v>
@@ -5065,39 +5117,39 @@
         <v>25</v>
       </c>
       <c r="M39" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O39" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s">
+        <v>373</v>
+      </c>
+      <c r="C40" t="s">
+        <v>366</v>
+      </c>
+      <c r="D40" t="s">
         <v>391</v>
       </c>
-      <c r="C40" t="s">
-        <v>384</v>
-      </c>
-      <c r="D40" t="s">
-        <v>409</v>
-      </c>
       <c r="G40" s="9" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I40" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J40" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K40" t="s">
         <v>13</v>
@@ -5106,39 +5158,39 @@
         <v>25</v>
       </c>
       <c r="M40" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O40" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s">
+        <v>374</v>
+      </c>
+      <c r="C41" t="s">
+        <v>366</v>
+      </c>
+      <c r="D41" t="s">
         <v>392</v>
       </c>
-      <c r="C41" t="s">
-        <v>384</v>
-      </c>
-      <c r="D41" t="s">
-        <v>410</v>
-      </c>
       <c r="G41" s="9" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I41" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J41" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K41" t="s">
         <v>13</v>
@@ -5147,39 +5199,39 @@
         <v>25</v>
       </c>
       <c r="M41" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O41" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42" t="s">
+        <v>366</v>
+      </c>
+      <c r="D42" t="s">
         <v>393</v>
       </c>
-      <c r="C42" t="s">
-        <v>384</v>
-      </c>
-      <c r="D42" t="s">
-        <v>411</v>
-      </c>
       <c r="G42" s="9" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I42" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="J42" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="K42" t="s">
         <v>13</v>
@@ -5188,39 +5240,39 @@
         <v>25</v>
       </c>
       <c r="M42" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="O42" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="B43" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="C43" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="D43" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I43" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J43" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K43" t="s">
         <v>13</v>
@@ -5229,39 +5281,39 @@
         <v>25</v>
       </c>
       <c r="M43" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O43" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="C44" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="D44" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I44" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J44" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K44" t="s">
         <v>13</v>
@@ -5270,39 +5322,39 @@
         <v>25</v>
       </c>
       <c r="M44" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O44" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="C45" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="D45" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I45" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J45" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K45" t="s">
         <v>13</v>
@@ -5311,39 +5363,39 @@
         <v>25</v>
       </c>
       <c r="M45" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O45" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" t="s">
+        <v>420</v>
+      </c>
+      <c r="D46" t="s">
+        <v>425</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I46" t="s">
+        <v>162</v>
+      </c>
+      <c r="J46" t="s">
         <v>279</v>
-      </c>
-      <c r="C46" t="s">
-        <v>439</v>
-      </c>
-      <c r="D46" t="s">
-        <v>444</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I46" t="s">
-        <v>173</v>
-      </c>
-      <c r="J46" t="s">
-        <v>296</v>
       </c>
       <c r="K46" t="s">
         <v>13</v>
@@ -5352,39 +5404,39 @@
         <v>25</v>
       </c>
       <c r="M46" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O46" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="C47" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="D47" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I47" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="J47" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K47" t="s">
         <v>13</v>
@@ -5393,34 +5445,34 @@
         <v>25</v>
       </c>
       <c r="M47" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="O47" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="B48" s="10"/>
       <c r="D48" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F48" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="G48" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I48" t="s">
         <v>36</v>
@@ -5435,45 +5487,45 @@
         <v>25</v>
       </c>
       <c r="M48" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O48" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P48" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q48" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="R48" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S48" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="D49" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F49" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I49" t="s">
         <v>36</v>
@@ -5488,26 +5540,243 @@
         <v>25</v>
       </c>
       <c r="M49" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O49" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q49" t="s">
+        <v>454</v>
+      </c>
+      <c r="R49" t="s">
+        <v>76</v>
+      </c>
+      <c r="S49" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>473</v>
+      </c>
+      <c r="D50" t="s">
         <v>474</v>
       </c>
-      <c r="R49" t="s">
-        <v>81</v>
-      </c>
-      <c r="S49" t="s">
+      <c r="E50" t="s">
+        <v>66</v>
+      </c>
+      <c r="F50" t="s">
         <v>475</v>
       </c>
+      <c r="G50" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I50" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K50" t="s">
+        <v>13</v>
+      </c>
+      <c r="L50" t="s">
+        <v>25</v>
+      </c>
+      <c r="M50" t="s">
+        <v>437</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O50" t="s">
+        <v>438</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>476</v>
+      </c>
+      <c r="R50" t="s">
+        <v>76</v>
+      </c>
+      <c r="S50" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>478</v>
+      </c>
+      <c r="D51" t="s">
+        <v>485</v>
+      </c>
+      <c r="E51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F51" t="s">
+        <v>487</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51" t="s">
+        <v>11</v>
+      </c>
+      <c r="K51" t="s">
+        <v>13</v>
+      </c>
+      <c r="L51" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" t="s">
+        <v>437</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" t="s">
+        <v>438</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>491</v>
+      </c>
+      <c r="R51" t="s">
+        <v>76</v>
+      </c>
+      <c r="S51" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>483</v>
+      </c>
+      <c r="D52" t="s">
+        <v>479</v>
+      </c>
+      <c r="E52" t="s">
+        <v>66</v>
+      </c>
+      <c r="F52" t="s">
+        <v>480</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I52" t="s">
+        <v>10</v>
+      </c>
+      <c r="J52" t="s">
+        <v>123</v>
+      </c>
+      <c r="K52" t="s">
+        <v>13</v>
+      </c>
+      <c r="L52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" t="s">
+        <v>437</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O52" t="s">
+        <v>438</v>
+      </c>
+      <c r="P52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>481</v>
+      </c>
+      <c r="R52" t="s">
+        <v>76</v>
+      </c>
+      <c r="S52" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>484</v>
+      </c>
+      <c r="D53" t="s">
+        <v>486</v>
+      </c>
+      <c r="E53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53" t="s">
+        <v>488</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I53" t="s">
+        <v>10</v>
+      </c>
+      <c r="J53" t="s">
+        <v>123</v>
+      </c>
+      <c r="K53" t="s">
+        <v>13</v>
+      </c>
+      <c r="L53" t="s">
+        <v>25</v>
+      </c>
+      <c r="M53" t="s">
+        <v>437</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O53" t="s">
+        <v>438</v>
+      </c>
+      <c r="P53" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>489</v>
+      </c>
+      <c r="R53" t="s">
+        <v>76</v>
+      </c>
+      <c r="S53" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="D54" s="3"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S15" xr:uid="{C0837104-CD0C-4055-94B3-0A98F94F86E8}"/>
@@ -5540,19 +5809,19 @@
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>1</v>
@@ -5561,13 +5830,13 @@
         <v>2</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>15</v>
@@ -5588,10 +5857,10 @@
         <v>42</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
@@ -5599,28 +5868,28 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>464</v>
       </c>
       <c r="H2" s="7">
         <v>0.25</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J2" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="K2" t="s">
         <v>13</v>
@@ -5629,13 +5898,13 @@
         <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N2" t="s">
         <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P2" t="s">
         <v>44</v>
@@ -5649,25 +5918,25 @@
         <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H3" s="7">
         <v>0.25</v>
       </c>
       <c r="I3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="J3" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="K3" t="s">
         <v>13</v>
@@ -5676,45 +5945,45 @@
         <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="O3" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P3" t="s">
         <v>44</v>
       </c>
       <c r="Q3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H4" s="7">
         <v>0.25</v>
       </c>
       <c r="I4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="J4" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="K4" t="s">
         <v>13</v>
@@ -5723,45 +5992,45 @@
         <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="O4" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P4" t="s">
         <v>44</v>
       </c>
       <c r="Q4" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="E5" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="F5" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>219</v>
+        <v>458</v>
       </c>
       <c r="H5" s="9">
         <v>0.1</v>
       </c>
       <c r="I5" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="J5" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="K5" t="s">
         <v>13</v>
@@ -5770,42 +6039,42 @@
         <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N5" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="O5" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P5" t="s">
         <v>44</v>
       </c>
       <c r="Q5" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>229</v>
+        <v>472</v>
       </c>
       <c r="I6" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="J6" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
@@ -5814,19 +6083,19 @@
         <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="N6" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="O6" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="P6" t="s">
         <v>44</v>
       </c>
       <c r="Q6" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/Librairies/TEP-AltiumLib-Passives-RLC.xlsx
+++ b/Librairies/TEP-AltiumLib-Passives-RLC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/Altium/243-TEP_Altium-Lib/Librairies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1595" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBF0353B-B995-417F-8815-1524ADBCECDB}"/>
+  <xr:revisionPtr revIDLastSave="1600" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67D1AD32-6B5E-4CA3-88EF-6BBB2E4DD030}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="16490" windowHeight="10260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="430" windowWidth="16490" windowHeight="10260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cap" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="503">
   <si>
     <t>Comment</t>
   </si>
@@ -1546,6 +1546,12 @@
   </si>
   <si>
     <t>L_4040[1515]</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>25%</t>
   </si>
 </sst>
 </file>
@@ -5935,8 +5941,8 @@
       <c r="I2" t="s">
         <v>462</v>
       </c>
-      <c r="J2" s="7">
-        <v>0.25</v>
+      <c r="J2" s="7" t="s">
+        <v>502</v>
       </c>
       <c r="K2" t="s">
         <v>495</v>
@@ -5982,8 +5988,8 @@
       <c r="I3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J3" s="7">
-        <v>0.25</v>
+      <c r="J3" s="7" t="s">
+        <v>502</v>
       </c>
       <c r="K3" t="s">
         <v>140</v>
@@ -6029,8 +6035,8 @@
       <c r="I4" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J4" s="7">
-        <v>0.25</v>
+      <c r="J4" s="7" t="s">
+        <v>502</v>
       </c>
       <c r="K4" t="s">
         <v>144</v>
@@ -6076,8 +6082,8 @@
       <c r="I5" t="s">
         <v>456</v>
       </c>
-      <c r="J5" s="9">
-        <v>0.1</v>
+      <c r="J5" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="K5" t="s">
         <v>205</v>
@@ -6167,8 +6173,8 @@
       <c r="I7" t="s">
         <v>462</v>
       </c>
-      <c r="J7" s="9">
-        <v>0.3</v>
+      <c r="J7" s="7" t="s">
+        <v>501</v>
       </c>
       <c r="K7" t="s">
         <v>493</v>
